--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,22 +408,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>34.09795</v>
+      </c>
+      <c r="C2">
+        <v>84.73161</v>
+      </c>
+      <c r="D2">
+        <v>74.45341999999999</v>
+      </c>
+      <c r="F2">
         <v>34.43346</v>
       </c>
-      <c r="C2">
-        <v>34.09795</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>89.18628</v>
       </c>
-      <c r="E2">
-        <v>84.73161</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>93.80689</v>
-      </c>
-      <c r="G2">
-        <v>74.45341999999999</v>
       </c>
     </row>
     <row r="3">
@@ -433,28 +433,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>54.26189</v>
+      </c>
+      <c r="C3">
+        <v>94.93701</v>
+      </c>
+      <c r="D3">
+        <v>80.78274999999999</v>
+      </c>
+      <c r="E3">
+        <v>37.1637</v>
+      </c>
+      <c r="F3">
         <v>54.42869</v>
       </c>
-      <c r="C3">
-        <v>54.26189</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>101.141</v>
       </c>
-      <c r="E3">
-        <v>94.93701</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>103.0232</v>
       </c>
-      <c r="G3">
-        <v>80.78274999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>57.28454</v>
-      </c>
-      <c r="I3">
-        <v>37.1637</v>
       </c>
     </row>
     <row r="4">
@@ -464,28 +464,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>56.09206</v>
+      </c>
+      <c r="C4">
+        <v>94.39037</v>
+      </c>
+      <c r="D4">
+        <v>80.07559000000001</v>
+      </c>
+      <c r="E4">
+        <v>30.88698</v>
+      </c>
+      <c r="F4">
         <v>56.26836</v>
       </c>
-      <c r="C4">
-        <v>56.09206</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.5408</v>
       </c>
-      <c r="E4">
-        <v>94.39037</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>104.0227</v>
       </c>
-      <c r="G4">
-        <v>80.07559000000001</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>46.35253</v>
-      </c>
-      <c r="I4">
-        <v>30.88698</v>
       </c>
     </row>
     <row r="5">
@@ -495,28 +495,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>53.56604</v>
+      </c>
+      <c r="C5">
+        <v>94.63330000000001</v>
+      </c>
+      <c r="D5">
+        <v>78.86032</v>
+      </c>
+      <c r="E5">
+        <v>36.23703</v>
+      </c>
+      <c r="F5">
         <v>53.8677</v>
       </c>
-      <c r="C5">
-        <v>53.56604</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>100.5036</v>
       </c>
-      <c r="E5">
-        <v>94.63330000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>100.3909</v>
       </c>
-      <c r="G5">
-        <v>78.86032</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>54.66108</v>
-      </c>
-      <c r="I5">
-        <v>36.23703</v>
       </c>
     </row>
     <row r="6">
@@ -526,28 +526,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>56.60139</v>
+      </c>
+      <c r="C6">
+        <v>94.76734</v>
+      </c>
+      <c r="D6">
+        <v>80.22884000000001</v>
+      </c>
+      <c r="E6">
+        <v>35.01237</v>
+      </c>
+      <c r="F6">
         <v>56.75932</v>
       </c>
-      <c r="C6">
-        <v>56.60139</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>100.7746</v>
       </c>
-      <c r="E6">
-        <v>94.76734</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>103.8398</v>
       </c>
-      <c r="G6">
-        <v>80.22884000000001</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>53.20869</v>
-      </c>
-      <c r="I6">
-        <v>35.01237</v>
       </c>
     </row>
     <row r="7">
@@ -557,28 +557,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>45.47475</v>
+      </c>
+      <c r="C7">
+        <v>90.57353999999999</v>
+      </c>
+      <c r="D7">
+        <v>78.68091</v>
+      </c>
+      <c r="E7">
+        <v>34.66742</v>
+      </c>
+      <c r="F7">
         <v>45.88235</v>
       </c>
-      <c r="C7">
-        <v>45.47475</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>95.90327000000001</v>
       </c>
-      <c r="E7">
-        <v>90.57353999999999</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>102.8487</v>
       </c>
-      <c r="G7">
-        <v>78.68091</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>55.10525</v>
-      </c>
-      <c r="I7">
-        <v>34.66742</v>
       </c>
     </row>
     <row r="8">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>52.30787</v>
+      </c>
+      <c r="C8">
+        <v>96.00252999999999</v>
+      </c>
+      <c r="D8">
+        <v>83.06647</v>
+      </c>
+      <c r="E8">
+        <v>42.91753</v>
+      </c>
+      <c r="F8">
         <v>52.97863</v>
       </c>
-      <c r="C8">
-        <v>52.30787</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>100.615</v>
       </c>
-      <c r="E8">
-        <v>96.00252999999999</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>100.4367</v>
       </c>
-      <c r="G8">
-        <v>83.06647</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>60.82096</v>
-      </c>
-      <c r="I8">
-        <v>42.91753</v>
       </c>
     </row>
     <row r="9">
@@ -619,28 +619,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>36.18538</v>
+      </c>
+      <c r="C9">
+        <v>87.35697999999999</v>
+      </c>
+      <c r="D9">
+        <v>77.57056</v>
+      </c>
+      <c r="E9">
+        <v>29.08201</v>
+      </c>
+      <c r="F9">
         <v>36.44682</v>
       </c>
-      <c r="C9">
-        <v>36.18538</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>91.10984000000001</v>
       </c>
-      <c r="E9">
-        <v>87.35697999999999</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>96.47177000000001</v>
       </c>
-      <c r="G9">
-        <v>77.57056</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>46.29947</v>
-      </c>
-      <c r="I9">
-        <v>29.08201</v>
       </c>
     </row>
     <row r="10">
@@ -650,28 +650,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>48.77316</v>
+      </c>
+      <c r="C10">
+        <v>93.53156</v>
+      </c>
+      <c r="D10">
+        <v>82.69637</v>
+      </c>
+      <c r="E10">
+        <v>44.0912</v>
+      </c>
+      <c r="F10">
         <v>48.92339</v>
       </c>
-      <c r="C10">
-        <v>48.77316</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>97.41504999999999</v>
       </c>
-      <c r="E10">
-        <v>93.53156</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>102.1571</v>
       </c>
-      <c r="G10">
-        <v>82.69637</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>69.04303</v>
-      </c>
-      <c r="I10">
-        <v>44.0912</v>
       </c>
     </row>
     <row r="11">
@@ -681,28 +681,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>50.79325</v>
+      </c>
+      <c r="C11">
+        <v>95.38052</v>
+      </c>
+      <c r="D11">
+        <v>83.18973</v>
+      </c>
+      <c r="E11">
+        <v>46.41576</v>
+      </c>
+      <c r="F11">
         <v>51.15683</v>
       </c>
-      <c r="C11">
-        <v>50.79325</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.3147</v>
       </c>
-      <c r="E11">
-        <v>95.38052</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>102.799</v>
       </c>
-      <c r="G11">
-        <v>83.18973</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>70.23895</v>
-      </c>
-      <c r="I11">
-        <v>46.41576</v>
       </c>
     </row>
     <row r="12">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>59.44101</v>
+      </c>
+      <c r="C12">
+        <v>95.37815000000001</v>
+      </c>
+      <c r="D12">
+        <v>79.47169</v>
+      </c>
+      <c r="E12">
+        <v>36.15702</v>
+      </c>
+      <c r="F12">
         <v>59.75037</v>
       </c>
-      <c r="C12">
-        <v>59.44101</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>102.117</v>
       </c>
-      <c r="E12">
-        <v>95.37815000000001</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>103.0641</v>
       </c>
-      <c r="G12">
-        <v>79.47169</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>54.82586</v>
-      </c>
-      <c r="I12">
-        <v>36.15702</v>
       </c>
     </row>
     <row r="13">
@@ -743,28 +743,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>59.9218</v>
+      </c>
+      <c r="C13">
+        <v>95.84321</v>
+      </c>
+      <c r="D13">
+        <v>75.37219</v>
+      </c>
+      <c r="E13">
+        <v>29.49453</v>
+      </c>
+      <c r="F13">
         <v>60.1564</v>
       </c>
-      <c r="C13">
-        <v>59.9218</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>103.9882</v>
       </c>
-      <c r="E13">
-        <v>95.84321</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>100.861</v>
       </c>
-      <c r="G13">
-        <v>75.37219</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>42.54367</v>
-      </c>
-      <c r="I13">
-        <v>29.49453</v>
       </c>
     </row>
     <row r="14">
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>46.09883</v>
+      </c>
+      <c r="C14">
+        <v>93.23914000000001</v>
+      </c>
+      <c r="D14">
+        <v>87.05882</v>
+      </c>
+      <c r="E14">
+        <v>62.80469</v>
+      </c>
+      <c r="F14">
         <v>48.42328</v>
       </c>
-      <c r="C14">
-        <v>46.09883</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>96.75561999999999</v>
       </c>
-      <c r="E14">
-        <v>93.23914000000001</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>99.4902</v>
       </c>
-      <c r="G14">
-        <v>87.05882</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>83.01006</v>
-      </c>
-      <c r="I14">
-        <v>62.80469</v>
       </c>
     </row>
     <row r="15">
@@ -805,28 +805,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.42888</v>
+      </c>
+      <c r="C15">
+        <v>93.05612000000001</v>
+      </c>
+      <c r="D15">
+        <v>86.65031999999999</v>
+      </c>
+      <c r="E15">
+        <v>67.55125</v>
+      </c>
+      <c r="F15">
         <v>31.67458</v>
       </c>
-      <c r="C15">
-        <v>29.42888</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>96.59303</v>
       </c>
-      <c r="E15">
-        <v>93.05612000000001</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>97.41013</v>
       </c>
-      <c r="G15">
-        <v>86.65031999999999</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>85.99507</v>
-      </c>
-      <c r="I15">
-        <v>67.55125</v>
       </c>
     </row>
     <row r="16">
@@ -836,28 +836,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>40.603</v>
+      </c>
+      <c r="C16">
+        <v>93.24122</v>
+      </c>
+      <c r="D16">
+        <v>86.39767000000001</v>
+      </c>
+      <c r="E16">
+        <v>67.22044</v>
+      </c>
+      <c r="F16">
         <v>44.49789</v>
       </c>
-      <c r="C16">
-        <v>40.603</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>98.48302</v>
       </c>
-      <c r="E16">
-        <v>93.24122</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>101.4592</v>
       </c>
-      <c r="G16">
-        <v>86.39767000000001</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>76.66133000000001</v>
-      </c>
-      <c r="I16">
-        <v>67.22044</v>
       </c>
     </row>
     <row r="17">
@@ -867,28 +867,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>55.49959</v>
+      </c>
+      <c r="C17">
+        <v>94.83991</v>
+      </c>
+      <c r="D17">
+        <v>78.11245</v>
+      </c>
+      <c r="E17">
+        <v>30.02764</v>
+      </c>
+      <c r="F17">
         <v>55.74462</v>
       </c>
-      <c r="C17">
-        <v>55.49959</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>101.5764</v>
       </c>
-      <c r="E17">
-        <v>94.83991</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>105.3852</v>
       </c>
-      <c r="G17">
-        <v>78.11245</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>45.70802</v>
-      </c>
-      <c r="I17">
-        <v>30.02764</v>
       </c>
     </row>
     <row r="18">
@@ -898,28 +898,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>52.78627</v>
+      </c>
+      <c r="C18">
+        <v>94.03358</v>
+      </c>
+      <c r="D18">
+        <v>80.55777</v>
+      </c>
+      <c r="E18">
+        <v>37.20593</v>
+      </c>
+      <c r="F18">
         <v>53.12091</v>
       </c>
-      <c r="C18">
-        <v>52.78627</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>99.78095</v>
       </c>
-      <c r="E18">
-        <v>94.03358</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>104.3028</v>
       </c>
-      <c r="G18">
-        <v>80.55777</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>56.0713</v>
-      </c>
-      <c r="I18">
-        <v>37.20593</v>
       </c>
     </row>
     <row r="19">
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>49.15406</v>
+      </c>
+      <c r="C19">
+        <v>94.09533</v>
+      </c>
+      <c r="D19">
+        <v>81.78337000000001</v>
+      </c>
+      <c r="E19">
+        <v>46.24399</v>
+      </c>
+      <c r="F19">
         <v>49.66675</v>
       </c>
-      <c r="C19">
-        <v>49.15406</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>98.92995999999999</v>
       </c>
-      <c r="E19">
-        <v>94.09533</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>101.7323</v>
       </c>
-      <c r="G19">
-        <v>81.78337000000001</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>72.40536</v>
-      </c>
-      <c r="I19">
-        <v>46.24399</v>
       </c>
     </row>
     <row r="20">
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>49.45501</v>
+      </c>
+      <c r="C20">
+        <v>95.88800999999999</v>
+      </c>
+      <c r="D20">
+        <v>83.67214</v>
+      </c>
+      <c r="E20">
+        <v>49.05654</v>
+      </c>
+      <c r="F20">
         <v>49.6868</v>
       </c>
-      <c r="C20">
-        <v>49.45501</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>100.7634</v>
       </c>
-      <c r="E20">
-        <v>95.88800999999999</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>102.3814</v>
       </c>
-      <c r="G20">
-        <v>83.67214</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>72.53896</v>
-      </c>
-      <c r="I20">
-        <v>49.05654</v>
       </c>
     </row>
     <row r="21">
@@ -991,28 +991,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>34.35977</v>
+      </c>
+      <c r="C21">
+        <v>92.61908</v>
+      </c>
+      <c r="D21">
+        <v>85.62263</v>
+      </c>
+      <c r="E21">
+        <v>56.62897</v>
+      </c>
+      <c r="F21">
         <v>35.27792</v>
       </c>
-      <c r="C21">
-        <v>34.35977</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>95.51781</v>
       </c>
-      <c r="E21">
-        <v>92.61908</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>97.93112000000001</v>
       </c>
-      <c r="G21">
-        <v>85.62263</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>85.22618</v>
-      </c>
-      <c r="I21">
-        <v>56.62897</v>
       </c>
     </row>
     <row r="22">
@@ -1022,28 +1022,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>57.5981</v>
+      </c>
+      <c r="C22">
+        <v>95.09354999999999</v>
+      </c>
+      <c r="D22">
+        <v>81.48502000000001</v>
+      </c>
+      <c r="E22">
+        <v>38.51479</v>
+      </c>
+      <c r="F22">
         <v>57.90097</v>
       </c>
-      <c r="C22">
-        <v>57.5981</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>100.0896</v>
       </c>
-      <c r="E22">
-        <v>95.09354999999999</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>106.0317</v>
       </c>
-      <c r="G22">
-        <v>81.48502000000001</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>59.28257</v>
-      </c>
-      <c r="I22">
-        <v>38.51479</v>
       </c>
     </row>
     <row r="23">
@@ -1053,28 +1053,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>55.30368</v>
+      </c>
+      <c r="C23">
+        <v>94.69833</v>
+      </c>
+      <c r="D23">
+        <v>81.93082</v>
+      </c>
+      <c r="E23">
+        <v>43.67262</v>
+      </c>
+      <c r="F23">
         <v>55.93432</v>
       </c>
-      <c r="C23">
-        <v>55.30368</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>100.2064</v>
       </c>
-      <c r="E23">
-        <v>94.69833</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>102.6937</v>
       </c>
-      <c r="G23">
-        <v>81.93082</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>60.8821</v>
-      </c>
-      <c r="I23">
-        <v>43.67262</v>
       </c>
     </row>
     <row r="24">
@@ -1084,28 +1084,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.68196</v>
+      </c>
+      <c r="C24">
+        <v>91.19574</v>
+      </c>
+      <c r="D24">
+        <v>86.55056</v>
+      </c>
+      <c r="E24">
+        <v>62.23958</v>
+      </c>
+      <c r="F24">
         <v>28.38576</v>
       </c>
-      <c r="C24">
-        <v>26.68196</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>93.79371999999999</v>
       </c>
-      <c r="E24">
-        <v>91.19574</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>97.21819000000001</v>
       </c>
-      <c r="G24">
-        <v>86.55056</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>94.60841000000001</v>
-      </c>
-      <c r="I24">
-        <v>62.23958</v>
       </c>
     </row>
     <row r="25">
@@ -1115,28 +1115,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>52.00135</v>
+      </c>
+      <c r="C25">
+        <v>95.5403</v>
+      </c>
+      <c r="D25">
+        <v>82.46581</v>
+      </c>
+      <c r="E25">
+        <v>40.25999</v>
+      </c>
+      <c r="F25">
         <v>52.22654</v>
       </c>
-      <c r="C25">
-        <v>52.00135</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>100.2565</v>
       </c>
-      <c r="E25">
-        <v>95.5403</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>102.7424</v>
       </c>
-      <c r="G25">
-        <v>82.46581</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>60.17592</v>
-      </c>
-      <c r="I25">
-        <v>40.25999</v>
       </c>
     </row>
     <row r="26">
@@ -1146,28 +1146,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>50.07283</v>
+      </c>
+      <c r="C26">
+        <v>95.76827</v>
+      </c>
+      <c r="D26">
+        <v>82.5372</v>
+      </c>
+      <c r="E26">
+        <v>40.71626</v>
+      </c>
+      <c r="F26">
         <v>50.27309</v>
       </c>
-      <c r="C26">
-        <v>50.07283</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>101.0355</v>
       </c>
-      <c r="E26">
-        <v>95.76827</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>96.38393000000001</v>
       </c>
-      <c r="G26">
-        <v>82.5372</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>58.43448</v>
-      </c>
-      <c r="I26">
-        <v>40.71626</v>
       </c>
     </row>
     <row r="27">
@@ -1177,28 +1177,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>48.13008</v>
+      </c>
+      <c r="C27">
+        <v>92.77665</v>
+      </c>
+      <c r="D27">
+        <v>80.75817000000001</v>
+      </c>
+      <c r="E27">
+        <v>36.47348</v>
+      </c>
+      <c r="F27">
         <v>48.31591</v>
       </c>
-      <c r="C27">
-        <v>48.13008</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>97.06263</v>
       </c>
-      <c r="E27">
-        <v>92.77665</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>101.3654</v>
       </c>
-      <c r="G27">
-        <v>80.75817000000001</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>58.12893</v>
-      </c>
-      <c r="I27">
-        <v>36.47348</v>
       </c>
     </row>
     <row r="28">
@@ -1208,28 +1208,28 @@
         </is>
       </c>
       <c r="B28">
+        <v>49.05853</v>
+      </c>
+      <c r="C28">
+        <v>92.41853</v>
+      </c>
+      <c r="D28">
+        <v>77.97060999999999</v>
+      </c>
+      <c r="E28">
+        <v>33.43802</v>
+      </c>
+      <c r="F28">
         <v>49.27821</v>
       </c>
-      <c r="C28">
-        <v>49.05853</v>
-      </c>
-      <c r="D28">
+      <c r="G28">
         <v>97.25434</v>
       </c>
-      <c r="E28">
-        <v>92.41853</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>98.68254</v>
       </c>
-      <c r="G28">
-        <v>77.97060999999999</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>51.65972</v>
-      </c>
-      <c r="I28">
-        <v>33.43802</v>
       </c>
     </row>
     <row r="29">
@@ -1239,28 +1239,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>59.54426</v>
+      </c>
+      <c r="C29">
+        <v>95.06137</v>
+      </c>
+      <c r="D29">
+        <v>80.33656000000001</v>
+      </c>
+      <c r="E29">
+        <v>33.69527</v>
+      </c>
+      <c r="F29">
         <v>59.78233</v>
       </c>
-      <c r="C29">
-        <v>59.54426</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>100.505</v>
       </c>
-      <c r="E29">
-        <v>95.06137</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>99.34302</v>
       </c>
-      <c r="G29">
-        <v>80.33656000000001</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>51.3172</v>
-      </c>
-      <c r="I29">
-        <v>33.69527</v>
       </c>
     </row>
     <row r="30">
@@ -1270,28 +1270,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>54.50776</v>
+      </c>
+      <c r="C30">
+        <v>94.48166999999999</v>
+      </c>
+      <c r="D30">
+        <v>81.25797</v>
+      </c>
+      <c r="E30">
+        <v>39.28676</v>
+      </c>
+      <c r="F30">
         <v>54.90708</v>
       </c>
-      <c r="C30">
-        <v>54.50776</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>100.4542</v>
       </c>
-      <c r="E30">
-        <v>94.48166999999999</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>103.3362</v>
       </c>
-      <c r="G30">
-        <v>81.25797</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>61.21017</v>
-      </c>
-      <c r="I30">
-        <v>39.28676</v>
       </c>
     </row>
     <row r="31">
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>38.89706</v>
+      </c>
+      <c r="C31">
+        <v>92.37209</v>
+      </c>
+      <c r="D31">
+        <v>84.66083999999999</v>
+      </c>
+      <c r="E31">
+        <v>48.43225</v>
+      </c>
+      <c r="F31">
         <v>39.375</v>
       </c>
-      <c r="C31">
-        <v>38.89706</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>96.20174</v>
       </c>
-      <c r="E31">
-        <v>92.37209</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>102.2538</v>
       </c>
-      <c r="G31">
-        <v>84.66083999999999</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>79.48862</v>
-      </c>
-      <c r="I31">
-        <v>48.43225</v>
       </c>
     </row>
     <row r="32">
@@ -1332,28 +1332,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>53.74335</v>
+      </c>
+      <c r="C32">
+        <v>95.02807</v>
+      </c>
+      <c r="D32">
+        <v>78.83987</v>
+      </c>
+      <c r="E32">
+        <v>32.87096</v>
+      </c>
+      <c r="F32">
         <v>54.18375</v>
       </c>
-      <c r="C32">
-        <v>53.74335</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>102.1537</v>
       </c>
-      <c r="E32">
-        <v>95.02807</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>104.3505</v>
       </c>
-      <c r="G32">
-        <v>78.83987</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>49.47739</v>
-      </c>
-      <c r="I32">
-        <v>32.87096</v>
       </c>
     </row>
     <row r="33">
@@ -1363,28 +1363,28 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.94528</v>
+      </c>
+      <c r="C33">
+        <v>91.32881999999999</v>
+      </c>
+      <c r="D33">
+        <v>87.82816</v>
+      </c>
+      <c r="E33">
+        <v>72.46129999999999</v>
+      </c>
+      <c r="F33">
         <v>28.65392</v>
       </c>
-      <c r="C33">
-        <v>25.94528</v>
-      </c>
-      <c r="D33">
+      <c r="G33">
         <v>94.77432</v>
       </c>
-      <c r="E33">
-        <v>91.32881999999999</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>96.63484</v>
       </c>
-      <c r="G33">
-        <v>87.82816</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>85.45654</v>
-      </c>
-      <c r="I33">
-        <v>72.46129999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1394,28 +1394,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>53.66514</v>
+      </c>
+      <c r="C34">
+        <v>96.17769</v>
+      </c>
+      <c r="D34">
+        <v>81.47686</v>
+      </c>
+      <c r="E34">
+        <v>43.32661</v>
+      </c>
+      <c r="F34">
         <v>53.87865</v>
       </c>
-      <c r="C34">
-        <v>53.66514</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>101.8089</v>
       </c>
-      <c r="E34">
-        <v>96.17769</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>101.5386</v>
       </c>
-      <c r="G34">
-        <v>81.47686</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>64.19486999999999</v>
-      </c>
-      <c r="I34">
-        <v>43.32661</v>
       </c>
     </row>
     <row r="35">
@@ -1425,28 +1425,28 @@
         </is>
       </c>
       <c r="B35">
+        <v>56.65215</v>
+      </c>
+      <c r="C35">
+        <v>95.27235</v>
+      </c>
+      <c r="D35">
+        <v>86.05914</v>
+      </c>
+      <c r="E35">
+        <v>45.71292</v>
+      </c>
+      <c r="F35">
         <v>57.18433</v>
       </c>
-      <c r="C35">
-        <v>56.65215</v>
-      </c>
-      <c r="D35">
+      <c r="G35">
         <v>98.938</v>
       </c>
-      <c r="E35">
-        <v>95.27235</v>
-      </c>
-      <c r="F35">
+      <c r="H35">
         <v>105.1298</v>
       </c>
-      <c r="G35">
-        <v>86.05914</v>
-      </c>
-      <c r="H35">
+      <c r="I35">
         <v>63.38667</v>
-      </c>
-      <c r="I35">
-        <v>45.71292</v>
       </c>
     </row>
     <row r="36">
@@ -1456,28 +1456,28 @@
         </is>
       </c>
       <c r="B36">
+        <v>56.35492</v>
+      </c>
+      <c r="C36">
+        <v>93.42403</v>
+      </c>
+      <c r="D36">
+        <v>83.83839</v>
+      </c>
+      <c r="E36">
+        <v>37.80838</v>
+      </c>
+      <c r="F36">
         <v>56.67466</v>
       </c>
-      <c r="C36">
-        <v>56.35492</v>
-      </c>
-      <c r="D36">
+      <c r="G36">
         <v>97.73242999999999</v>
       </c>
-      <c r="E36">
-        <v>93.42403</v>
-      </c>
-      <c r="F36">
+      <c r="H36">
         <v>100.8081</v>
       </c>
-      <c r="G36">
-        <v>83.83839</v>
-      </c>
-      <c r="H36">
+      <c r="I36">
         <v>53.98738</v>
-      </c>
-      <c r="I36">
-        <v>37.80838</v>
       </c>
     </row>
     <row r="37">
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="B37">
+        <v>51.08943</v>
+      </c>
+      <c r="C37">
+        <v>93.62130999999999</v>
+      </c>
+      <c r="D37">
+        <v>81.43655</v>
+      </c>
+      <c r="E37">
+        <v>39.6952</v>
+      </c>
+      <c r="F37">
         <v>52.66992</v>
       </c>
-      <c r="C37">
-        <v>51.08943</v>
-      </c>
-      <c r="D37">
+      <c r="G37">
         <v>100.7421</v>
       </c>
-      <c r="E37">
-        <v>93.62130999999999</v>
-      </c>
-      <c r="F37">
+      <c r="H37">
         <v>99.18402</v>
       </c>
-      <c r="G37">
-        <v>81.43655</v>
-      </c>
-      <c r="H37">
+      <c r="I37">
         <v>54.27947</v>
-      </c>
-      <c r="I37">
-        <v>39.6952</v>
       </c>
     </row>
     <row r="38">
@@ -1518,28 +1518,28 @@
         </is>
       </c>
       <c r="B38">
+        <v>49.7637</v>
+      </c>
+      <c r="C38">
+        <v>95.46294</v>
+      </c>
+      <c r="D38">
+        <v>79.97393</v>
+      </c>
+      <c r="E38">
+        <v>33.33651</v>
+      </c>
+      <c r="F38">
         <v>49.96481</v>
       </c>
-      <c r="C38">
-        <v>49.7637</v>
-      </c>
-      <c r="D38">
+      <c r="G38">
         <v>100.6207</v>
       </c>
-      <c r="E38">
-        <v>95.46294</v>
-      </c>
-      <c r="F38">
+      <c r="H38">
         <v>97.62099000000001</v>
       </c>
-      <c r="G38">
-        <v>79.97393</v>
-      </c>
-      <c r="H38">
+      <c r="I38">
         <v>50.15743</v>
-      </c>
-      <c r="I38">
-        <v>33.33651</v>
       </c>
     </row>
     <row r="39">
@@ -1549,28 +1549,28 @@
         </is>
       </c>
       <c r="B39">
+        <v>55.17891</v>
+      </c>
+      <c r="C39">
+        <v>97.10899999999999</v>
+      </c>
+      <c r="D39">
+        <v>83.92856999999999</v>
+      </c>
+      <c r="E39">
+        <v>33.19068</v>
+      </c>
+      <c r="F39">
         <v>55.36723</v>
       </c>
-      <c r="C39">
-        <v>55.17891</v>
-      </c>
-      <c r="D39">
+      <c r="G39">
         <v>102.5592</v>
       </c>
-      <c r="E39">
-        <v>97.10899999999999</v>
-      </c>
-      <c r="F39">
+      <c r="H39">
         <v>107.0489</v>
       </c>
-      <c r="G39">
-        <v>83.92856999999999</v>
-      </c>
-      <c r="H39">
+      <c r="I39">
         <v>48.9301</v>
-      </c>
-      <c r="I39">
-        <v>33.19068</v>
       </c>
     </row>
     <row r="40">
@@ -1580,28 +1580,28 @@
         </is>
       </c>
       <c r="B40">
+        <v>54.9952</v>
+      </c>
+      <c r="C40">
+        <v>95.31513</v>
+      </c>
+      <c r="D40">
+        <v>81.59435000000001</v>
+      </c>
+      <c r="E40">
+        <v>36.51813</v>
+      </c>
+      <c r="F40">
         <v>55.20829</v>
       </c>
-      <c r="C40">
-        <v>54.9952</v>
-      </c>
-      <c r="D40">
+      <c r="G40">
         <v>100.5974</v>
       </c>
-      <c r="E40">
-        <v>95.31513</v>
-      </c>
-      <c r="F40">
+      <c r="H40">
         <v>103.4007</v>
       </c>
-      <c r="G40">
-        <v>81.59435000000001</v>
-      </c>
-      <c r="H40">
+      <c r="I40">
         <v>53.30563</v>
-      </c>
-      <c r="I40">
-        <v>36.51813</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="B41">
+        <v>49.67038</v>
+      </c>
+      <c r="C41">
+        <v>95.49448</v>
+      </c>
+      <c r="D41">
+        <v>84.46957</v>
+      </c>
+      <c r="E41">
+        <v>39.69902</v>
+      </c>
+      <c r="F41">
         <v>50.01798</v>
       </c>
-      <c r="C41">
-        <v>49.67038</v>
-      </c>
-      <c r="D41">
+      <c r="G41">
         <v>100.7915</v>
       </c>
-      <c r="E41">
-        <v>95.49448</v>
-      </c>
-      <c r="F41">
+      <c r="H41">
         <v>102.5391</v>
       </c>
-      <c r="G41">
-        <v>84.46957</v>
-      </c>
-      <c r="H41">
+      <c r="I41">
         <v>57.15783</v>
-      </c>
-      <c r="I41">
-        <v>39.69902</v>
       </c>
     </row>
     <row r="42">
@@ -1642,28 +1642,28 @@
         </is>
       </c>
       <c r="B42">
+        <v>54.81557</v>
+      </c>
+      <c r="C42">
+        <v>95.65922</v>
+      </c>
+      <c r="D42">
+        <v>83.63319</v>
+      </c>
+      <c r="E42">
+        <v>42.52245</v>
+      </c>
+      <c r="F42">
         <v>55.48156</v>
       </c>
-      <c r="C42">
-        <v>54.81557</v>
-      </c>
-      <c r="D42">
+      <c r="G42">
         <v>99.90282000000001</v>
       </c>
-      <c r="E42">
-        <v>95.65922</v>
-      </c>
-      <c r="F42">
+      <c r="H42">
         <v>105.2815</v>
       </c>
-      <c r="G42">
-        <v>83.63319</v>
-      </c>
-      <c r="H42">
+      <c r="I42">
         <v>59.72276</v>
-      </c>
-      <c r="I42">
-        <v>42.52245</v>
       </c>
     </row>
     <row r="43">
@@ -1673,28 +1673,28 @@
         </is>
       </c>
       <c r="B43">
+        <v>53.46119</v>
+      </c>
+      <c r="C43">
+        <v>95.79338</v>
+      </c>
+      <c r="D43">
+        <v>83.50976</v>
+      </c>
+      <c r="E43">
+        <v>36.05914</v>
+      </c>
+      <c r="F43">
         <v>53.73516</v>
       </c>
-      <c r="C43">
-        <v>53.46119</v>
-      </c>
-      <c r="D43">
+      <c r="G43">
         <v>101.2104</v>
       </c>
-      <c r="E43">
-        <v>95.79338</v>
-      </c>
-      <c r="F43">
+      <c r="H43">
         <v>97.31828</v>
       </c>
-      <c r="G43">
-        <v>83.50976</v>
-      </c>
-      <c r="H43">
+      <c r="I43">
         <v>49.74487</v>
-      </c>
-      <c r="I43">
-        <v>36.05914</v>
       </c>
     </row>
     <row r="44">
@@ -1704,28 +1704,28 @@
         </is>
       </c>
       <c r="B44">
+        <v>53.56104</v>
+      </c>
+      <c r="C44">
+        <v>95.78455</v>
+      </c>
+      <c r="D44">
+        <v>82.08456</v>
+      </c>
+      <c r="E44">
+        <v>34.8842</v>
+      </c>
+      <c r="F44">
         <v>53.78731</v>
       </c>
-      <c r="C44">
-        <v>53.56104</v>
-      </c>
-      <c r="D44">
+      <c r="G44">
         <v>101.0539</v>
       </c>
-      <c r="E44">
-        <v>95.78455</v>
-      </c>
-      <c r="F44">
+      <c r="H44">
         <v>102.665</v>
       </c>
-      <c r="G44">
-        <v>82.08456</v>
-      </c>
-      <c r="H44">
+      <c r="I44">
         <v>48.56711</v>
-      </c>
-      <c r="I44">
-        <v>34.8842</v>
       </c>
     </row>
     <row r="45">
@@ -1735,28 +1735,28 @@
         </is>
       </c>
       <c r="B45">
+        <v>49.30663</v>
+      </c>
+      <c r="C45">
+        <v>94.47641</v>
+      </c>
+      <c r="D45">
+        <v>86.37681000000001</v>
+      </c>
+      <c r="E45">
+        <v>25.94595</v>
+      </c>
+      <c r="F45">
         <v>49.61479</v>
       </c>
-      <c r="C45">
-        <v>49.30663</v>
-      </c>
-      <c r="D45">
+      <c r="G45">
         <v>100.2301</v>
       </c>
-      <c r="E45">
-        <v>94.47641</v>
-      </c>
-      <c r="F45">
+      <c r="H45">
         <v>105.7971</v>
       </c>
-      <c r="G45">
-        <v>86.37681000000001</v>
-      </c>
-      <c r="H45">
+      <c r="I45">
         <v>39.13514</v>
-      </c>
-      <c r="I45">
-        <v>25.94595</v>
       </c>
     </row>
     <row r="46">
@@ -1766,28 +1766,28 @@
         </is>
       </c>
       <c r="B46">
+        <v>56.62835</v>
+      </c>
+      <c r="C46">
+        <v>96.0827</v>
+      </c>
+      <c r="D46">
+        <v>81.50722</v>
+      </c>
+      <c r="E46">
+        <v>39.9124</v>
+      </c>
+      <c r="F46">
         <v>56.66667</v>
       </c>
-      <c r="C46">
-        <v>56.62835</v>
-      </c>
-      <c r="D46">
+      <c r="G46">
         <v>101.9314</v>
       </c>
-      <c r="E46">
-        <v>96.0827</v>
-      </c>
-      <c r="F46">
+      <c r="H46">
         <v>109.2464</v>
       </c>
-      <c r="G46">
-        <v>81.50722</v>
-      </c>
-      <c r="H46">
+      <c r="I46">
         <v>57.40487</v>
-      </c>
-      <c r="I46">
-        <v>39.9124</v>
       </c>
     </row>
     <row r="47">
@@ -1797,28 +1797,28 @@
         </is>
       </c>
       <c r="B47">
+        <v>55.83567</v>
+      </c>
+      <c r="C47">
+        <v>95.91969</v>
+      </c>
+      <c r="D47">
+        <v>86.50694</v>
+      </c>
+      <c r="E47">
+        <v>35.4017</v>
+      </c>
+      <c r="F47">
         <v>56.11578</v>
       </c>
-      <c r="C47">
-        <v>55.83567</v>
-      </c>
-      <c r="D47">
+      <c r="G47">
         <v>101.0363</v>
       </c>
-      <c r="E47">
-        <v>95.91969</v>
-      </c>
-      <c r="F47">
+      <c r="H47">
         <v>98.61286</v>
       </c>
-      <c r="G47">
-        <v>86.50694</v>
-      </c>
-      <c r="H47">
+      <c r="I47">
         <v>47.74657</v>
-      </c>
-      <c r="I47">
-        <v>35.4017</v>
       </c>
     </row>
     <row r="48">
@@ -1827,23 +1827,23 @@
           <t>San Pedro</t>
         </is>
       </c>
+      <c r="C48">
+        <v>96.40492</v>
+      </c>
       <c r="D48">
+        <v>87.17949</v>
+      </c>
+      <c r="E48">
+        <v>29.55832</v>
+      </c>
+      <c r="G48">
         <v>101.3245</v>
       </c>
-      <c r="E48">
-        <v>96.40492</v>
-      </c>
-      <c r="F48">
+      <c r="H48">
         <v>96.88643999999999</v>
       </c>
-      <c r="G48">
-        <v>87.17949</v>
-      </c>
-      <c r="H48">
+      <c r="I48">
         <v>37.03284</v>
-      </c>
-      <c r="I48">
-        <v>29.55832</v>
       </c>
     </row>
     <row r="49">
@@ -1853,28 +1853,28 @@
         </is>
       </c>
       <c r="B49">
+        <v>54.49122</v>
+      </c>
+      <c r="C49">
+        <v>95.18944</v>
+      </c>
+      <c r="D49">
+        <v>82.52336</v>
+      </c>
+      <c r="E49">
+        <v>39.41554</v>
+      </c>
+      <c r="F49">
         <v>54.98551</v>
       </c>
-      <c r="C49">
-        <v>54.49122</v>
-      </c>
-      <c r="D49">
+      <c r="G49">
         <v>100.5857</v>
       </c>
-      <c r="E49">
-        <v>95.18944</v>
-      </c>
-      <c r="F49">
+      <c r="H49">
         <v>100.2804</v>
       </c>
-      <c r="G49">
-        <v>82.52336</v>
-      </c>
-      <c r="H49">
+      <c r="I49">
         <v>57.24638</v>
-      </c>
-      <c r="I49">
-        <v>39.41554</v>
       </c>
     </row>
     <row r="50">
@@ -1884,28 +1884,28 @@
         </is>
       </c>
       <c r="B50">
+        <v>60.37025</v>
+      </c>
+      <c r="C50">
+        <v>95.38924</v>
+      </c>
+      <c r="D50">
+        <v>81.35275</v>
+      </c>
+      <c r="E50">
+        <v>33.5157</v>
+      </c>
+      <c r="F50">
         <v>60.52714</v>
       </c>
-      <c r="C50">
-        <v>60.37025</v>
-      </c>
-      <c r="D50">
+      <c r="G50">
         <v>99.83781</v>
       </c>
-      <c r="E50">
-        <v>95.38924</v>
-      </c>
-      <c r="F50">
+      <c r="H50">
         <v>104.3682</v>
       </c>
-      <c r="G50">
-        <v>81.35275</v>
-      </c>
-      <c r="H50">
+      <c r="I50">
         <v>48.45385</v>
-      </c>
-      <c r="I50">
-        <v>33.5157</v>
       </c>
     </row>
     <row r="51">
@@ -1915,28 +1915,28 @@
         </is>
       </c>
       <c r="B51">
+        <v>58.0507</v>
+      </c>
+      <c r="C51">
+        <v>95.44776</v>
+      </c>
+      <c r="D51">
+        <v>85.12241</v>
+      </c>
+      <c r="E51">
+        <v>35.39126</v>
+      </c>
+      <c r="F51">
         <v>58.55052</v>
       </c>
-      <c r="C51">
-        <v>58.0507</v>
-      </c>
-      <c r="D51">
+      <c r="G51">
         <v>99.62687</v>
       </c>
-      <c r="E51">
-        <v>95.44776</v>
-      </c>
-      <c r="F51">
+      <c r="H51">
         <v>103.6252</v>
       </c>
-      <c r="G51">
-        <v>85.12241</v>
-      </c>
-      <c r="H51">
+      <c r="I51">
         <v>48.55183</v>
-      </c>
-      <c r="I51">
-        <v>35.39126</v>
       </c>
     </row>
     <row r="52">
@@ -1946,28 +1946,28 @@
         </is>
       </c>
       <c r="B52">
+        <v>50.20685</v>
+      </c>
+      <c r="C52">
+        <v>95.00132000000001</v>
+      </c>
+      <c r="D52">
+        <v>82.39809</v>
+      </c>
+      <c r="E52">
+        <v>38.43683</v>
+      </c>
+      <c r="F52">
         <v>50.38888</v>
       </c>
-      <c r="C52">
-        <v>50.20685</v>
-      </c>
-      <c r="D52">
+      <c r="G52">
         <v>99.76197000000001</v>
       </c>
-      <c r="E52">
-        <v>95.00132000000001</v>
-      </c>
-      <c r="F52">
+      <c r="H52">
         <v>104.3145</v>
       </c>
-      <c r="G52">
-        <v>82.39809</v>
-      </c>
-      <c r="H52">
+      <c r="I52">
         <v>57.6151</v>
-      </c>
-      <c r="I52">
-        <v>38.43683</v>
       </c>
     </row>
     <row r="53">
@@ -1977,28 +1977,28 @@
         </is>
       </c>
       <c r="B53">
+        <v>54.91526</v>
+      </c>
+      <c r="C53">
+        <v>95.72313</v>
+      </c>
+      <c r="D53">
+        <v>83.29698</v>
+      </c>
+      <c r="E53">
+        <v>40.30418</v>
+      </c>
+      <c r="F53">
         <v>55.14576</v>
       </c>
-      <c r="C53">
-        <v>54.91526</v>
-      </c>
-      <c r="D53">
+      <c r="G53">
         <v>100.4221</v>
       </c>
-      <c r="E53">
-        <v>95.72313</v>
-      </c>
-      <c r="F53">
+      <c r="H53">
         <v>102.6899</v>
       </c>
-      <c r="G53">
-        <v>83.29698</v>
-      </c>
-      <c r="H53">
+      <c r="I53">
         <v>58.14639</v>
-      </c>
-      <c r="I53">
-        <v>40.30418</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:42</t>
+    <t xml:space="preserve">2026-08-02 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:41</t>
+    <t xml:space="preserve">2026-08-05 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:33</t>
+    <t xml:space="preserve">2026-08-16 09:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:45</t>
+    <t xml:space="preserve">2026-08-19 11:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:40</t>
+    <t xml:space="preserve">2026-08-28 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:23</t>
+    <t xml:space="preserve">2026-09-06 17:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
